--- a/config/Mangler_rominformasjon.xlsx
+++ b/config/Mangler_rominformasjon.xlsx
@@ -27009,7 +27009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="37.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -27078,6 +27078,27 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Alle typenavn som begynner med Aspirasjonrør</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Alle trekkerør bend som er 25 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Alle typenavn som begynner med 3D Detaljpil nummer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
